--- a/data/filtered/china_scifi.xlsx
+++ b/data/filtered/china_scifi.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I212"/>
+  <dimension ref="A1:N212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,31 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>是否春节档</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>是否国庆档</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>是否五一档</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>是否暑期档</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>是否普通周末</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>详情链接</t>
         </is>
       </c>
@@ -498,7 +523,22 @@
           <t>1982-06-25</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1291839/</t>
         </is>
@@ -539,7 +579,22 @@
           <t>2023-01-22</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35267208/</t>
         </is>
@@ -580,7 +635,22 @@
           <t>2013-01-31</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3530403/</t>
         </is>
@@ -621,7 +691,22 @@
           <t>2023-04-01</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34941536/</t>
         </is>
@@ -662,7 +747,22 @@
           <t>2019-02-05</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26266893/</t>
         </is>
@@ -703,7 +803,22 @@
           <t>2013-05-01</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3231742/</t>
         </is>
@@ -744,7 +859,22 @@
           <t>1995-08-19</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1300498/</t>
         </is>
@@ -785,7 +915,22 @@
           <t>1998-01-17</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1300303/</t>
         </is>
@@ -826,7 +971,22 @@
           <t>1986</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1299687/</t>
         </is>
@@ -867,7 +1027,22 @@
           <t>2015-09-12</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25706773/</t>
         </is>
@@ -908,7 +1083,22 @@
           <t>2014-10-24</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24404677/</t>
         </is>
@@ -949,7 +1139,22 @@
           <t>1988</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1440283/</t>
         </is>
@@ -990,7 +1195,22 @@
           <t>2010-01-23</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4217526/</t>
         </is>
@@ -1031,7 +1251,22 @@
           <t>2008-01-30</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1961963/</t>
         </is>
@@ -1072,7 +1307,22 @@
           <t>2024-08-02</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26816104/</t>
         </is>
@@ -1113,7 +1363,22 @@
           <t>2018-11-09</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3168101/</t>
         </is>
@@ -1154,7 +1419,22 @@
           <t>1990</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1528848/</t>
         </is>
@@ -1195,7 +1475,22 @@
           <t>2023-01-22</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36123159/</t>
         </is>
@@ -1236,7 +1531,22 @@
           <t>2006-09-29</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1780168/</t>
         </is>
@@ -1277,7 +1587,22 @@
           <t>2021-04-30</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30229667/</t>
         </is>
@@ -1318,7 +1643,22 @@
           <t>2019-01-04</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26394152/</t>
         </is>
@@ -1359,7 +1699,22 @@
           <t>2025-01-29</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36970301/</t>
         </is>
@@ -1400,7 +1755,22 @@
           <t>2024-02-10</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36438166/</t>
         </is>
@@ -1441,7 +1811,22 @@
           <t>1993-09-30</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1295858/</t>
         </is>
@@ -1482,7 +1867,22 @@
           <t>2002-01-11</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1305386/</t>
         </is>
@@ -1523,7 +1923,22 @@
           <t>2017-08-25</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11502973/</t>
         </is>
@@ -1564,7 +1979,22 @@
           <t>2019-12-13</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30394535/</t>
         </is>
@@ -1605,7 +2035,22 @@
           <t>2012-09-28</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3179706/</t>
         </is>
@@ -1646,7 +2091,22 @@
           <t>2026-02-17</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36883105/</t>
         </is>
@@ -1687,7 +2147,22 @@
           <t>2009-10-23</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1917074/</t>
         </is>
@@ -1728,7 +2203,22 @@
           <t>2019-10-18</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3097572/</t>
         </is>
@@ -1769,7 +2259,22 @@
           <t>2021-01-15</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34962956/</t>
         </is>
@@ -1810,7 +2315,22 @@
           <t>1996-11-09</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1295746/</t>
         </is>
@@ -1851,7 +2371,22 @@
           <t>2019-12-05</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24716039/</t>
         </is>
@@ -1892,7 +2427,22 @@
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26967871/</t>
         </is>
@@ -1933,7 +2483,22 @@
           <t>2014-06-27</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/7054604/</t>
         </is>
@@ -1974,7 +2539,22 @@
           <t>2012-04-18</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3742937/</t>
         </is>
@@ -2015,7 +2595,22 @@
           <t>2014-04-18</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10810745/</t>
         </is>
@@ -2056,7 +2651,22 @@
           <t>2022-07-29</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35183042/</t>
         </is>
@@ -2097,7 +2707,22 @@
           <t>2016-07-02</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25955779/</t>
         </is>
@@ -2138,7 +2763,22 @@
           <t>2024-12-07</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36999844/</t>
         </is>
@@ -2179,7 +2819,22 @@
           <t>2005-09-29</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1427834/</t>
         </is>
@@ -2220,7 +2875,22 @@
           <t>2017-02-24</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20471852/</t>
         </is>
@@ -2261,7 +2931,22 @@
           <t>2025-11-22</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35416174/</t>
         </is>
@@ -2302,7 +2987,22 @@
           <t>1988-04-28</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1473078/</t>
         </is>
@@ -2343,7 +3043,22 @@
           <t>2019-02-05</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25986662/</t>
         </is>
@@ -2384,7 +3099,22 @@
           <t>2017-04-07</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25818101/</t>
         </is>
@@ -2425,7 +3155,22 @@
           <t>2014-10-01</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24372055/</t>
         </is>
@@ -2466,7 +3211,22 @@
           <t>1997</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1938923/</t>
         </is>
@@ -2507,7 +3267,22 @@
           <t>2015-09-15</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25838463/</t>
         </is>
@@ -2548,7 +3323,22 @@
           <t>2001-12-15</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1298065/</t>
         </is>
@@ -2589,7 +3379,22 @@
           <t>1990-03-30</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1292598/</t>
         </is>
@@ -2630,7 +3435,22 @@
           <t>1990</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1482688/</t>
         </is>
@@ -2671,7 +3491,22 @@
           <t>2002-03-28</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1306916/</t>
         </is>
@@ -2712,7 +3547,22 @@
           <t>2019-05-31</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25890017/</t>
         </is>
@@ -2753,7 +3603,22 @@
           <t>1989-08-18</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1293729/</t>
         </is>
@@ -2794,7 +3659,22 @@
           <t>2021-02-12</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34825886/</t>
         </is>
@@ -2835,7 +3715,22 @@
           <t>2022-08-05</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26353671/</t>
         </is>
@@ -2876,7 +3771,22 @@
           <t>2010-06-04</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4275444/</t>
         </is>
@@ -2917,7 +3827,22 @@
           <t>1992</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2259312/</t>
         </is>
@@ -2958,7 +3883,22 @@
           <t>1991-12-19</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="I62" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1301278/</t>
         </is>
@@ -2999,7 +3939,22 @@
           <t>1992-11-20</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I63" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1293452/</t>
         </is>
@@ -3040,7 +3995,22 @@
           <t>2023-09-28</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="I64" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35622477/</t>
         </is>
@@ -3081,7 +4051,22 @@
           <t>1987-01-22</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="I65" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1302799/</t>
         </is>
@@ -3122,7 +4107,22 @@
           <t>1986-01-11</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="I66" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1828616/</t>
         </is>
@@ -3163,7 +4163,22 @@
           <t>2021-10-15</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="I67" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35115642/</t>
         </is>
@@ -3204,7 +4219,22 @@
           <t>1986-09-17</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="I68" t="n">
+        <v>0</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1308237/</t>
         </is>
@@ -3245,7 +4275,22 @@
           <t>2018-11-23</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="I69" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26219713/</t>
         </is>
@@ -3286,7 +4331,22 @@
           <t>1991-05-31</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5120686/</t>
         </is>
@@ -3327,7 +4387,22 @@
           <t>2013-03-14</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I71" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/7161695/</t>
         </is>
@@ -3368,7 +4443,22 @@
           <t>2022-07-16</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I72" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27599400/</t>
         </is>
@@ -3409,7 +4499,22 @@
           <t>2018-08-10</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I73" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
+        <v>1</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26426194/</t>
         </is>
@@ -3450,7 +4555,22 @@
           <t>2004-12-04</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="I74" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1</v>
+      </c>
+      <c r="N74" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1422931/</t>
         </is>
@@ -3491,7 +4611,22 @@
           <t>2013-11-22</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10604087/</t>
         </is>
@@ -3532,7 +4667,22 @@
           <t>2016-07-16</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="I76" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26780023/</t>
         </is>
@@ -3573,7 +4723,22 @@
           <t>2020-10-23</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I77" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30141681/</t>
         </is>
@@ -3614,7 +4779,22 @@
           <t>2004-08-19</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="I78" t="n">
+        <v>0</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0</v>
+      </c>
+      <c r="N78" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1389891/</t>
         </is>
@@ -3655,7 +4835,22 @@
           <t>1976-07-24</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I79" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2988846/</t>
         </is>
@@ -3696,7 +4891,22 @@
           <t>2023-07-08</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="I80" t="n">
+        <v>0</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36065713/</t>
         </is>
@@ -3737,7 +4947,22 @@
           <t>1988-03-10</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="I81" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1304465/</t>
         </is>
@@ -3778,7 +5003,22 @@
           <t>1992-10-22</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="I82" t="n">
+        <v>0</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1484138/</t>
         </is>
@@ -3819,7 +5059,22 @@
           <t>2019-07-19</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>1</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27200988/</t>
         </is>
@@ -3860,7 +5115,22 @@
           <t>2007-08-31</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="I84" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" t="n">
+        <v>1</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0</v>
+      </c>
+      <c r="N84" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2052973/</t>
         </is>
@@ -3901,7 +5171,22 @@
           <t>2017-10-10</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I85" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27133264/</t>
         </is>
@@ -3942,7 +5227,22 @@
           <t>2020-07-24</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I86" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>1</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4830483/</t>
         </is>
@@ -3983,7 +5283,22 @@
           <t>1989</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I87" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1300509/</t>
         </is>
@@ -4024,7 +5339,22 @@
           <t>2018-03-23</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20435622/</t>
         </is>
@@ -4065,7 +5395,22 @@
           <t>2023-12-30</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1</v>
+      </c>
+      <c r="N89" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26769592/</t>
         </is>
@@ -4106,7 +5451,22 @@
           <t>1980</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="I90" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1440854/</t>
         </is>
@@ -4147,7 +5507,22 @@
           <t>2009-08-18</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="I91" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>1</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3990500/</t>
         </is>
@@ -4188,7 +5563,22 @@
           <t>2002-03-28</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="I92" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1306983/</t>
         </is>
@@ -4229,7 +5619,22 @@
           <t>1998-11-08</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="I93" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>1</v>
+      </c>
+      <c r="N93" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2157280/</t>
         </is>
@@ -4270,7 +5675,22 @@
           <t>2017-02-24</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="I94" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11526817/</t>
         </is>
@@ -4311,7 +5731,22 @@
           <t>1975-08-01</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="I95" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1308377/</t>
         </is>
@@ -4352,7 +5787,22 @@
           <t>2022-03-25</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="I96" t="n">
+        <v>0</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26825482/</t>
         </is>
@@ -4393,7 +5843,22 @@
           <t>2024-10-03</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="I97" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/37060861/</t>
         </is>
@@ -4430,7 +5895,22 @@
           <t>2025-05-01</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="I98" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/37298398/</t>
         </is>
@@ -4471,7 +5951,22 @@
           <t>2012-03-31</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="I99" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1</v>
+      </c>
+      <c r="N99" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/11516686/</t>
         </is>
@@ -4512,7 +6007,22 @@
           <t>2023-12-30</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="I100" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>1</v>
+      </c>
+      <c r="N100" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35496650/</t>
         </is>
@@ -4553,7 +6063,22 @@
           <t>2015-08-07</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="I101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" t="n">
+        <v>1</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/21943062/</t>
         </is>
@@ -4594,7 +6119,22 @@
           <t>2021-10-01</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="I102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" t="n">
+        <v>1</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30382416/</t>
         </is>
@@ -4635,7 +6175,22 @@
           <t>2018-06-16</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="I103" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1</v>
+      </c>
+      <c r="N103" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26791910/</t>
         </is>
@@ -4676,7 +6231,22 @@
           <t>2021-08-31</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I104" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="n">
+        <v>1</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30402063/</t>
         </is>
@@ -4717,7 +6287,22 @@
           <t>2006</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="I105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1830457/</t>
         </is>
@@ -4758,7 +6343,22 @@
           <t>2012-01-24</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="I106" t="n">
+        <v>1</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6799156/</t>
         </is>
@@ -4799,7 +6399,22 @@
           <t>1988</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="I107" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3727334/</t>
         </is>
@@ -4840,7 +6455,22 @@
           <t>2015-08-06</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="I108" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" t="n">
+        <v>1</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26331608/</t>
         </is>
@@ -4881,7 +6511,22 @@
           <t>2023-08-04</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="I109" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" t="n">
+        <v>1</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34882958/</t>
         </is>
@@ -4922,7 +6567,22 @@
           <t>2017-10-14</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="I110" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1</v>
+      </c>
+      <c r="N110" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5324813/</t>
         </is>
@@ -4963,7 +6623,22 @@
           <t>2018-09-08</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="I111" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>1</v>
+      </c>
+      <c r="N111" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26707077/</t>
         </is>
@@ -5004,7 +6679,22 @@
           <t>1991-03-22</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="I112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1308900/</t>
         </is>
@@ -5045,7 +6735,22 @@
           <t>1987-04-03</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="I113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1303392/</t>
         </is>
@@ -5086,7 +6791,22 @@
           <t>2001-12-07</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1308331/</t>
         </is>
@@ -5127,7 +6847,22 @@
           <t>2017-06-23</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="I115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25824686/</t>
         </is>
@@ -5168,7 +6903,22 @@
           <t>2024-01-20</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="I116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1</v>
+      </c>
+      <c r="N116" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36314920/</t>
         </is>
@@ -5209,7 +6959,22 @@
           <t>2020-08-06</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="I117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" t="n">
+        <v>1</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0</v>
+      </c>
+      <c r="N117" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34661803/</t>
         </is>
@@ -5250,7 +7015,22 @@
           <t>1991</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="I118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0</v>
+      </c>
+      <c r="N118" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1529245/</t>
         </is>
@@ -5291,7 +7071,22 @@
           <t>2018-01-26</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="I119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26724807/</t>
         </is>
@@ -5332,7 +7127,22 @@
           <t>1987</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="I120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4172534/</t>
         </is>
@@ -5369,7 +7179,22 @@
           <t>2017-08-30</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
+      <c r="I121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L121" t="n">
+        <v>1</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26897547/</t>
         </is>
@@ -5410,7 +7235,22 @@
           <t>2019-02-22</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
+      <c r="I122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0</v>
+      </c>
+      <c r="N122" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30420068/</t>
         </is>
@@ -5451,7 +7291,22 @@
           <t>2022-09-01</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
+      <c r="I123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35936420/</t>
         </is>
@@ -5492,7 +7347,22 @@
           <t>2002-12-24</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1306935/</t>
         </is>
@@ -5533,7 +7403,22 @@
           <t>1993-03-17</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1308891/</t>
         </is>
@@ -5574,7 +7459,22 @@
           <t>2015-12-04</t>
         </is>
       </c>
-      <c r="I126" t="inlineStr">
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26277156/</t>
         </is>
@@ -5615,7 +7515,22 @@
           <t>2019-06-05</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34458481/</t>
         </is>
@@ -5656,7 +7571,22 @@
           <t>2021-02-26</t>
         </is>
       </c>
-      <c r="I128" t="inlineStr">
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34460775/</t>
         </is>
@@ -5693,7 +7623,22 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35710037/</t>
         </is>
@@ -5734,7 +7679,22 @@
           <t>2018-08-30</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>1</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30299388/</t>
         </is>
@@ -5775,7 +7735,22 @@
           <t>1963</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20266727/</t>
         </is>
@@ -5816,7 +7791,22 @@
           <t>2017-06-29</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26667056/</t>
         </is>
@@ -5857,7 +7847,22 @@
           <t>2010-08-06</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr">
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>1</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3874981/</t>
         </is>
@@ -5898,7 +7903,22 @@
           <t>2021-02-12</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
+      <c r="I134" t="n">
+        <v>1</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0</v>
+      </c>
+      <c r="N134" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35017085/</t>
         </is>
@@ -5939,7 +7959,22 @@
           <t>2008-10-24</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr">
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3266407/</t>
         </is>
@@ -5980,7 +8015,22 @@
           <t>2017-12-22</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr">
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26729868/</t>
         </is>
@@ -6021,7 +8071,22 @@
           <t>2016-10-04</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr">
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>1</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26807960/</t>
         </is>
@@ -6062,7 +8127,22 @@
           <t>2019-11-28</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30481964/</t>
         </is>
@@ -6103,7 +8183,22 @@
           <t>2025-12-06</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr">
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>1</v>
+      </c>
+      <c r="N139" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30305568/</t>
         </is>
@@ -6144,7 +8239,22 @@
           <t>1977-08-11</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr">
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>1</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1306999/</t>
         </is>
@@ -6185,7 +8295,22 @@
           <t>2011-10-06</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr">
+      <c r="I141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" t="n">
+        <v>1</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/6796160/</t>
         </is>
@@ -6226,7 +8351,22 @@
           <t>1984-06-19</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr">
+      <c r="I142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0</v>
+      </c>
+      <c r="N142" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1533608/</t>
         </is>
@@ -6267,7 +8407,22 @@
           <t>2017-05-27</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
+      <c r="I143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="n">
+        <v>1</v>
+      </c>
+      <c r="N143" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24714697/</t>
         </is>
@@ -6308,7 +8463,22 @@
           <t>2020-07-05</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr">
+      <c r="I144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L144" t="n">
+        <v>1</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0</v>
+      </c>
+      <c r="N144" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24875519/</t>
         </is>
@@ -6349,7 +8519,22 @@
           <t>2024-05-01</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr">
+      <c r="I145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" t="n">
+        <v>1</v>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0</v>
+      </c>
+      <c r="N145" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36597039/</t>
         </is>
@@ -6390,7 +8575,22 @@
           <t>2017-05-12</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr">
+      <c r="I146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0</v>
+      </c>
+      <c r="N146" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25881615/</t>
         </is>
@@ -6431,7 +8631,22 @@
           <t>2019-09-29</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
+      <c r="I147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" t="n">
+        <v>1</v>
+      </c>
+      <c r="K147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0</v>
+      </c>
+      <c r="N147" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30128922/</t>
         </is>
@@ -6472,7 +8687,22 @@
           <t>2006-08-04</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
+      <c r="I148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L148" t="n">
+        <v>1</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1795037/</t>
         </is>
@@ -6513,7 +8743,22 @@
           <t>2018-01-26</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
+      <c r="I149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0</v>
+      </c>
+      <c r="N149" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27056322/</t>
         </is>
@@ -6550,7 +8795,22 @@
           <t>2012</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr">
+      <c r="I150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0</v>
+      </c>
+      <c r="N150" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/20431606/</t>
         </is>
@@ -6587,7 +8847,22 @@
           <t>2023-10-23</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
+      <c r="I151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36707486/</t>
         </is>
@@ -6628,7 +8903,22 @@
           <t>2022-12-25</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr">
+      <c r="I152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="n">
+        <v>1</v>
+      </c>
+      <c r="N152" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35295013/</t>
         </is>
@@ -6669,7 +8959,22 @@
           <t>1997-12-20</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr">
+      <c r="I153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>1</v>
+      </c>
+      <c r="N153" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1303715/</t>
         </is>
@@ -6706,7 +9011,22 @@
           <t>2010-08-04</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr">
+      <c r="I154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L154" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/5320222/</t>
         </is>
@@ -6747,7 +9067,22 @@
           <t>1983-02-12</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
+      <c r="I155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" t="n">
+        <v>0</v>
+      </c>
+      <c r="M155" t="n">
+        <v>1</v>
+      </c>
+      <c r="N155" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/1302011/</t>
         </is>
@@ -6788,7 +9123,22 @@
           <t>2022-07-15</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
+      <c r="I156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" t="n">
+        <v>1</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35168646/</t>
         </is>
@@ -6829,7 +9179,22 @@
           <t>2021-09-17</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
+      <c r="I157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35043230/</t>
         </is>
@@ -6870,7 +9235,22 @@
           <t>2017-05-26</t>
         </is>
       </c>
-      <c r="I158" t="inlineStr">
+      <c r="I158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27054033/</t>
         </is>
@@ -6911,7 +9291,22 @@
           <t>2013-08-23</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
+      <c r="I159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L159" t="n">
+        <v>1</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0</v>
+      </c>
+      <c r="N159" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24872197/</t>
         </is>
@@ -6952,7 +9347,22 @@
           <t>2016-07-07</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr">
+      <c r="I160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" t="n">
+        <v>1</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26602368/</t>
         </is>
@@ -6993,7 +9403,22 @@
           <t>2020-06-18</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
+      <c r="I161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0</v>
+      </c>
+      <c r="N161" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35089826/</t>
         </is>
@@ -7034,7 +9459,22 @@
           <t>2021-12-03</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr">
+      <c r="I162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0</v>
+      </c>
+      <c r="N162" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35248741/</t>
         </is>
@@ -7075,7 +9515,22 @@
           <t>2010-06-01</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
+      <c r="I163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3811388/</t>
         </is>
@@ -7116,7 +9571,22 @@
           <t>2010-03-30</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr">
+      <c r="I164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0</v>
+      </c>
+      <c r="N164" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/3329192/</t>
         </is>
@@ -7157,7 +9627,22 @@
           <t>2022-01-12</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr">
+      <c r="I165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L165" t="n">
+        <v>0</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35295101/</t>
         </is>
@@ -7198,7 +9683,22 @@
           <t>2022-03-04</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr">
+      <c r="I166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35268026/</t>
         </is>
@@ -7239,7 +9739,22 @@
           <t>2018-03-14</t>
         </is>
       </c>
-      <c r="I167" t="inlineStr">
+      <c r="I167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" t="n">
+        <v>0</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27052551/</t>
         </is>
@@ -7280,7 +9795,22 @@
           <t>2025-03-21</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr">
+      <c r="I168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" t="n">
+        <v>0</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0</v>
+      </c>
+      <c r="N168" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35559713/</t>
         </is>
@@ -7321,7 +9851,22 @@
           <t>2019-08-02</t>
         </is>
       </c>
-      <c r="I169" t="inlineStr">
+      <c r="I169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0</v>
+      </c>
+      <c r="N169" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34779698/</t>
         </is>
@@ -7362,7 +9907,22 @@
           <t>2019-04-28</t>
         </is>
       </c>
-      <c r="I170" t="inlineStr">
+      <c r="I170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K170" t="n">
+        <v>1</v>
+      </c>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0</v>
+      </c>
+      <c r="N170" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26921002/</t>
         </is>
@@ -7403,7 +9963,22 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr">
+      <c r="I171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0</v>
+      </c>
+      <c r="N171" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35515217/</t>
         </is>
@@ -7444,7 +10019,22 @@
           <t>2018-09-19</t>
         </is>
       </c>
-      <c r="I172" t="inlineStr">
+      <c r="I172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K172" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0</v>
+      </c>
+      <c r="N172" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30317800/</t>
         </is>
@@ -7485,7 +10075,22 @@
           <t>2018-03-02</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr">
+      <c r="I173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" t="n">
+        <v>0</v>
+      </c>
+      <c r="M173" t="n">
+        <v>0</v>
+      </c>
+      <c r="N173" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26836837/</t>
         </is>
@@ -7526,7 +10131,22 @@
           <t>2022-01-22</t>
         </is>
       </c>
-      <c r="I174" t="inlineStr">
+      <c r="I174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" t="n">
+        <v>1</v>
+      </c>
+      <c r="N174" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35447154/</t>
         </is>
@@ -7567,7 +10187,22 @@
           <t>2003</t>
         </is>
       </c>
-      <c r="I175" t="inlineStr">
+      <c r="I175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K175" t="n">
+        <v>0</v>
+      </c>
+      <c r="L175" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" t="n">
+        <v>0</v>
+      </c>
+      <c r="N175" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/4821044/</t>
         </is>
@@ -7608,7 +10243,22 @@
           <t>2021-07-16</t>
         </is>
       </c>
-      <c r="I176" t="inlineStr">
+      <c r="I176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K176" t="n">
+        <v>0</v>
+      </c>
+      <c r="L176" t="n">
+        <v>1</v>
+      </c>
+      <c r="M176" t="n">
+        <v>0</v>
+      </c>
+      <c r="N176" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27191370/</t>
         </is>
@@ -7649,7 +10299,22 @@
           <t>2020-03-10</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr">
+      <c r="I177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0</v>
+      </c>
+      <c r="N177" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26826370/</t>
         </is>
@@ -7690,7 +10355,22 @@
           <t>2020-11-27</t>
         </is>
       </c>
-      <c r="I178" t="inlineStr">
+      <c r="I178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0</v>
+      </c>
+      <c r="N178" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34868338/</t>
         </is>
@@ -7731,7 +10411,22 @@
           <t>2023-08-22</t>
         </is>
       </c>
-      <c r="I179" t="inlineStr">
+      <c r="I179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L179" t="n">
+        <v>1</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0</v>
+      </c>
+      <c r="N179" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35061128/</t>
         </is>
@@ -7772,7 +10467,22 @@
           <t>2020-01-27</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr">
+      <c r="I180" t="n">
+        <v>1</v>
+      </c>
+      <c r="J180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0</v>
+      </c>
+      <c r="N180" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34953858/</t>
         </is>
@@ -7813,7 +10523,22 @@
           <t>2019-04-30</t>
         </is>
       </c>
-      <c r="I181" t="inlineStr">
+      <c r="I181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K181" t="n">
+        <v>1</v>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30345341/</t>
         </is>
@@ -7854,7 +10579,22 @@
           <t>2009-03-14</t>
         </is>
       </c>
-      <c r="I182" t="inlineStr">
+      <c r="I182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K182" t="n">
+        <v>0</v>
+      </c>
+      <c r="L182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" t="n">
+        <v>1</v>
+      </c>
+      <c r="N182" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2310144/</t>
         </is>
@@ -7895,7 +10635,22 @@
           <t>2022-02-23</t>
         </is>
       </c>
-      <c r="I183" t="inlineStr">
+      <c r="I183" t="n">
+        <v>0</v>
+      </c>
+      <c r="J183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L183" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35043875/</t>
         </is>
@@ -7936,7 +10691,22 @@
           <t>2018-06-22</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr">
+      <c r="I184" t="n">
+        <v>0</v>
+      </c>
+      <c r="J184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K184" t="n">
+        <v>0</v>
+      </c>
+      <c r="L184" t="n">
+        <v>0</v>
+      </c>
+      <c r="M184" t="n">
+        <v>0</v>
+      </c>
+      <c r="N184" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26677141/</t>
         </is>
@@ -7977,7 +10747,22 @@
           <t>2023-10-14</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr">
+      <c r="I185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K185" t="n">
+        <v>0</v>
+      </c>
+      <c r="L185" t="n">
+        <v>0</v>
+      </c>
+      <c r="M185" t="n">
+        <v>1</v>
+      </c>
+      <c r="N185" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/36597293/</t>
         </is>
@@ -8018,7 +10803,22 @@
           <t>2021-09-03</t>
         </is>
       </c>
-      <c r="I186" t="inlineStr">
+      <c r="I186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L186" t="n">
+        <v>0</v>
+      </c>
+      <c r="M186" t="n">
+        <v>0</v>
+      </c>
+      <c r="N186" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35411088/</t>
         </is>
@@ -8059,7 +10859,22 @@
           <t>2017-11-01</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr">
+      <c r="I187" t="n">
+        <v>0</v>
+      </c>
+      <c r="J187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K187" t="n">
+        <v>0</v>
+      </c>
+      <c r="L187" t="n">
+        <v>0</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27180936/</t>
         </is>
@@ -8100,7 +10915,22 @@
           <t>2021-08-27</t>
         </is>
       </c>
-      <c r="I188" t="inlineStr">
+      <c r="I188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" t="n">
+        <v>1</v>
+      </c>
+      <c r="M188" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35027723/</t>
         </is>
@@ -8141,7 +10971,22 @@
           <t>2016-04-02</t>
         </is>
       </c>
-      <c r="I189" t="inlineStr">
+      <c r="I189" t="n">
+        <v>0</v>
+      </c>
+      <c r="J189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K189" t="n">
+        <v>0</v>
+      </c>
+      <c r="L189" t="n">
+        <v>0</v>
+      </c>
+      <c r="M189" t="n">
+        <v>1</v>
+      </c>
+      <c r="N189" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26655587/</t>
         </is>
@@ -8182,7 +11027,22 @@
           <t>2015-01-30</t>
         </is>
       </c>
-      <c r="I190" t="inlineStr">
+      <c r="I190" t="n">
+        <v>0</v>
+      </c>
+      <c r="J190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K190" t="n">
+        <v>0</v>
+      </c>
+      <c r="L190" t="n">
+        <v>0</v>
+      </c>
+      <c r="M190" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26285355/</t>
         </is>
@@ -8223,7 +11083,22 @@
           <t>2017-08-21</t>
         </is>
       </c>
-      <c r="I191" t="inlineStr">
+      <c r="I191" t="n">
+        <v>0</v>
+      </c>
+      <c r="J191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K191" t="n">
+        <v>0</v>
+      </c>
+      <c r="L191" t="n">
+        <v>1</v>
+      </c>
+      <c r="M191" t="n">
+        <v>0</v>
+      </c>
+      <c r="N191" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27118877/</t>
         </is>
@@ -8264,7 +11139,22 @@
           <t>2020-06-24</t>
         </is>
       </c>
-      <c r="I192" t="inlineStr">
+      <c r="I192" t="n">
+        <v>0</v>
+      </c>
+      <c r="J192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35092721/</t>
         </is>
@@ -8305,7 +11195,22 @@
           <t>2022-04-20</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
+      <c r="I193" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" t="n">
+        <v>0</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35860951/</t>
         </is>
@@ -8346,7 +11251,22 @@
           <t>2014</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
+      <c r="I194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" t="n">
+        <v>0</v>
+      </c>
+      <c r="M194" t="n">
+        <v>0</v>
+      </c>
+      <c r="N194" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/24753788/</t>
         </is>
@@ -8387,7 +11307,22 @@
           <t>2020-07-31</t>
         </is>
       </c>
-      <c r="I195" t="inlineStr">
+      <c r="I195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" t="n">
+        <v>1</v>
+      </c>
+      <c r="M195" t="n">
+        <v>0</v>
+      </c>
+      <c r="N195" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35154685/</t>
         </is>
@@ -8428,7 +11363,22 @@
           <t>2020-09-04</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr">
+      <c r="I196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" t="n">
+        <v>0</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0</v>
+      </c>
+      <c r="N196" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35196786/</t>
         </is>
@@ -8469,7 +11419,22 @@
           <t>2015-05-30</t>
         </is>
       </c>
-      <c r="I197" t="inlineStr">
+      <c r="I197" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" t="n">
+        <v>0</v>
+      </c>
+      <c r="M197" t="n">
+        <v>1</v>
+      </c>
+      <c r="N197" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26381387/</t>
         </is>
@@ -8510,7 +11475,22 @@
           <t>2020-09-11</t>
         </is>
       </c>
-      <c r="I198" t="inlineStr">
+      <c r="I198" t="n">
+        <v>0</v>
+      </c>
+      <c r="J198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L198" t="n">
+        <v>0</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34433857/</t>
         </is>
@@ -8551,7 +11531,22 @@
           <t>2021-12-02</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr">
+      <c r="I199" t="n">
+        <v>0</v>
+      </c>
+      <c r="J199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L199" t="n">
+        <v>0</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0</v>
+      </c>
+      <c r="N199" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/35295114/</t>
         </is>
@@ -8592,7 +11587,22 @@
           <t>2014-10-10</t>
         </is>
       </c>
-      <c r="I200" t="inlineStr">
+      <c r="I200" t="n">
+        <v>0</v>
+      </c>
+      <c r="J200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K200" t="n">
+        <v>0</v>
+      </c>
+      <c r="L200" t="n">
+        <v>0</v>
+      </c>
+      <c r="M200" t="n">
+        <v>0</v>
+      </c>
+      <c r="N200" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/25958914/</t>
         </is>
@@ -8633,7 +11643,22 @@
           <t>2017-02-01</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr">
+      <c r="I201" t="n">
+        <v>1</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K201" t="n">
+        <v>0</v>
+      </c>
+      <c r="L201" t="n">
+        <v>0</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26790117/</t>
         </is>
@@ -8674,7 +11699,22 @@
           <t>2019-01-18</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr">
+      <c r="I202" t="n">
+        <v>0</v>
+      </c>
+      <c r="J202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K202" t="n">
+        <v>0</v>
+      </c>
+      <c r="L202" t="n">
+        <v>0</v>
+      </c>
+      <c r="M202" t="n">
+        <v>0</v>
+      </c>
+      <c r="N202" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/30190607/</t>
         </is>
@@ -8715,7 +11755,22 @@
           <t>2020-02-07</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr">
+      <c r="I203" t="n">
+        <v>0</v>
+      </c>
+      <c r="J203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L203" t="n">
+        <v>0</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0</v>
+      </c>
+      <c r="N203" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/34951373/</t>
         </is>
@@ -8756,7 +11811,22 @@
           <t>2016-02-19</t>
         </is>
       </c>
-      <c r="I204" t="inlineStr">
+      <c r="I204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K204" t="n">
+        <v>0</v>
+      </c>
+      <c r="L204" t="n">
+        <v>0</v>
+      </c>
+      <c r="M204" t="n">
+        <v>0</v>
+      </c>
+      <c r="N204" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26730276/</t>
         </is>
@@ -8797,7 +11867,22 @@
           <t>2021-04-23</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr">
+      <c r="I205" t="n">
+        <v>0</v>
+      </c>
+      <c r="J205" t="n">
+        <v>0</v>
+      </c>
+      <c r="K205" t="n">
+        <v>0</v>
+      </c>
+      <c r="L205" t="n">
+        <v>0</v>
+      </c>
+      <c r="M205" t="n">
+        <v>0</v>
+      </c>
+      <c r="N205" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/33383459/</t>
         </is>
@@ -8838,7 +11923,22 @@
           <t>2016-01-29</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr">
+      <c r="I206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L206" t="n">
+        <v>0</v>
+      </c>
+      <c r="M206" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26279449/</t>
         </is>
@@ -8879,7 +11979,22 @@
           <t>2014-01-01</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr">
+      <c r="I207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K207" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" t="n">
+        <v>0</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/10756744/</t>
         </is>
@@ -8920,7 +12035,22 @@
           <t>2012-10-12</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr">
+      <c r="I208" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" t="n">
+        <v>0</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/2130529/</t>
         </is>
@@ -8961,7 +12091,22 @@
           <t>2024-10-01</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="n">
+        <v>1</v>
+      </c>
+      <c r="K209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L209" t="n">
+        <v>0</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0</v>
+      </c>
+      <c r="N209" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26747919/</t>
         </is>
@@ -9002,7 +12147,22 @@
           <t>2019-04-12</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr">
+      <c r="I210" t="n">
+        <v>0</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L210" t="n">
+        <v>0</v>
+      </c>
+      <c r="M210" t="n">
+        <v>0</v>
+      </c>
+      <c r="N210" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26850330/</t>
         </is>
@@ -9043,7 +12203,22 @@
           <t>2017-10-01</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr">
+      <c r="I211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" t="n">
+        <v>1</v>
+      </c>
+      <c r="K211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L211" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/27045442/</t>
         </is>
@@ -9084,7 +12259,22 @@
           <t>2019-08-09</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr">
+      <c r="I212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L212" t="n">
+        <v>1</v>
+      </c>
+      <c r="M212" t="n">
+        <v>0</v>
+      </c>
+      <c r="N212" t="inlineStr">
         <is>
           <t>https://movie.douban.com/subject/26581837/</t>
         </is>
